--- a/src/ii_skills/shared/excel_templates/07_sources_uses.xlsx
+++ b/src/ii_skills/shared/excel_templates/07_sources_uses.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,13 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,9 +43,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -48,18 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000A651"/>
-        <bgColor rgb="0000A651"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -67,20 +68,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="double"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,309 +453,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Sources &amp; Uses of Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>$ in millions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>VALUATION SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Source_Item</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Low_Case</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Mid_Case</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>High_Case</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Equity Issue</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AFFO</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I3" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Retained Interest</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>157</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>13.5x</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>14.5x</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15.5x</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Portfolio Debt</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>282</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Equity Value</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>297</v>
-      </c>
-      <c r="H5" t="n">
-        <v>319</v>
-      </c>
-      <c r="I5" t="n">
-        <v>341</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Senior Term Loan</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5.0x LTM EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sponsor Equity</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Management Rollover</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>$10M commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Total Sources</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>549</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>569</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>589</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>+ Net Debt</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>234</v>
-      </c>
-      <c r="H6" t="n">
-        <v>234</v>
-      </c>
-      <c r="I6" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="F7">
-        <f> Enterprise Value</f>
-        <v/>
-      </c>
-      <c r="G7" t="n">
-        <v>502</v>
-      </c>
-      <c r="H7" t="n">
-        <v>521</v>
-      </c>
-      <c r="I7" t="n">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="C10" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Use_Item</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Low_Case</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Mid_Case</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>High_Case</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>% of Total</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Purchase Price</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>488</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>507</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Transaction Costs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Debt Repayment</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="C15" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>11.0x LTM EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Transaction Fees</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3% of EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Financing Fees</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4% of debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>549</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>569</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>589</v>
-      </c>
+      <c r="C18" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B5:E5"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>